--- a/cleaning_forms/019_daily_office_cleaning_checklist--cleaning_forms.xlsx
+++ b/cleaning_forms/019_daily_office_cleaning_checklist--cleaning_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist</t>
+          <t>office_cleaning_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Office Cleaning Checklist</t>
+          <t>How often do you clean the office?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency</t>
+          <t>office_cleaning_tasks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How often do you clean the office</t>
+          <t>Office Cleaning Tasks</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,46 +561,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>office_cleaning_time</t>
+          <t>office_cleaner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How much time do you spend on office cleaning</t>
+          <t>Contact Office Cleaner</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>office_cleaning_note</t>
+          <t>office_cleaner_name</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,22 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_office_cleaner</t>
+          <t>office_cleaner_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Contact Office Cleaner</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Enter the name and contact information of the person responsible for office cleaning</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>office_cleaner_email</t>
+          <t>office_cleaner_phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Office Cleaner Email</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>office_cleaner_phone</t>
+          <t>office_cleaner_department</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Office Cleaner Phone</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>office_cleaner_name</t>
+          <t>office_cleaner_ext</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Office Cleaner Name</t>
+          <t>Extension</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>office_cleaner_title</t>
+          <t>office_cleaning_frequency_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Office Cleaner Title</t>
+          <t>How often do you perform the office cleaning tasks?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>office_cleaner_department</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office Cleaner Department</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>office_cleaner_ext</t>
+          <t>office_cleaning_checklist</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Office Cleaner Extension</t>
+          <t>Office Cleaning Checklist</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2</t>
+          <t>office_cleaning_frequency_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How often do you clean the office</t>
+          <t>Office Cleaning Frequency 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_2</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How often do you clean the office</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_3</t>
+          <t>office_cleaning_frequency_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How often do you clean the office</t>
+          <t>Office Cleaning Frequency 4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,85 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_4</t>
+          <t>office_cleaning_frequency_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How often do you clean the office</t>
+          <t>Office Cleaning Frequency 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>office_cleaning_checklist_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Office Cleaning Checklist</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>office_cleaning_checklist_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Office Cleaning Checklist</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -941,10 +868,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
@@ -969,442 +896,459 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_choices</t>
+          <t>office_cleaning_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dust_the_office</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dust the office</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_choices</t>
+          <t>office_cleaning_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>vacuum_the_office</t>
+          <t>every_week</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vacuum the office</t>
+          <t>Every week</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_choices</t>
+          <t>office_cleaning_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>disinfect_high-touch_areas</t>
+          <t>every_2_weeks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Disinfect high-touch areas</t>
+          <t>Every 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_choices</t>
+          <t>office_cleaning_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>every_day</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Every day</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_choices</t>
+          <t>office_cleaning_tasks_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>every_week</t>
+          <t>dust_the_floors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Every week</t>
+          <t>Dust the floors</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_choices</t>
+          <t>office_cleaning_tasks_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>every_2_weeks</t>
+          <t>vacuum_the_floors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Every 2 weeks</t>
+          <t>Vacuum the floors</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_choices</t>
+          <t>office_cleaning_tasks_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>disinfect_the_bathrooms</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Disinfect the bathrooms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_2_choices</t>
+          <t>office_cleaning_tasks_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>disinfect_the_kitchen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Disinfect the kitchen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_2_choices</t>
+          <t>office_cleaning_frequency_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_2_choices</t>
+          <t>office_cleaning_frequency_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_2_choices</t>
+          <t>office_cleaning_frequency_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_3_choices</t>
+          <t>office_cleaning_frequency_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_3_choices</t>
+          <t>office_cleaning_checklist_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>clean_the_office</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Clean the office</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_3_choices</t>
+          <t>office_cleaning_checklist_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>clean_the_break_room</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Clean the break room</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_3_choices</t>
+          <t>office_cleaning_checklist_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>clean_the_office_equipment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Clean the office equipment</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_4_choices</t>
+          <t>office_cleaning_checklist_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>disinfect_the_office</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Disinfect the office</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_4_choices</t>
+          <t>office_cleaning_frequency_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>office_cleaning_frequency_2_4_choices</t>
+          <t>office_cleaning_frequency_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_2_choices</t>
+          <t>office_cleaning_frequency_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>dust_the_floors</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dust the floors</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_2_choices</t>
+          <t>office_cleaning_frequency_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vacuum_the_floors</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vacuum the floors</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_2_choices</t>
+          <t>office_cleaning_frequency_4_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>disinfect_the_bathrooms</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Disinfect the bathrooms</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_2_choices</t>
+          <t>office_cleaning_frequency_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>disinfect_the_kitchen</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Disinfect the kitchen</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_3_choices</t>
+          <t>office_cleaning_frequency_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>clean_the_office</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Clean the office</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_3_choices</t>
+          <t>office_cleaning_frequency_4_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>clean_the_break_room</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Clean the break room</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_3_choices</t>
+          <t>office_cleaning_frequency_5_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>clean_the_office_equipment</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Clean the office equipment</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>office_cleaning_checklist_3_choices</t>
+          <t>office_cleaning_frequency_5_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>disinfect_the_office</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Disinfect the office</t>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>office_cleaning_frequency_5_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Never</t>
         </is>
       </c>
     </row>
